--- a/Impact Soundworks/Bravura Scoring Brass/xlsx/02 Solo.xlsx
+++ b/Impact Soundworks/Bravura Scoring Brass/xlsx/02 Solo.xlsx
@@ -39,6 +39,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -61,6 +76,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -89,6 +119,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -111,6 +156,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -139,6 +199,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -161,6 +236,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -189,6 +279,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -214,6 +319,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -230,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="159">
   <si>
     <t>Name</t>
   </si>
@@ -681,12 +801,39 @@
   <si>
     <t>Trill Min</t>
   </si>
+  <si>
+    <t>Expression Map Name</t>
+  </si>
+  <si>
+    <t>08 Solo Piccolo Trumpet</t>
+  </si>
+  <si>
+    <t>09 Solo Trumpet</t>
+  </si>
+  <si>
+    <t>10 Solo Flugelhorn</t>
+  </si>
+  <si>
+    <t>11 Solo Horn</t>
+  </si>
+  <si>
+    <t>12 Solo Trombone</t>
+  </si>
+  <si>
+    <t>13 Solo Tuba</t>
+  </si>
+  <si>
+    <t>14 Solo Orchestrator</t>
+  </si>
+  <si>
+    <t>15 Solo Chordmaker</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -731,8 +878,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -785,6 +939,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEEF4"/>
         <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -844,7 +1004,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -904,6 +1064,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -994,13 +1160,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1299,7 +1465,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1307,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -1320,100 +1486,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -1421,12 +1546,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -1434,13 +1555,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -1449,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -1461,13 +1582,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -1476,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -1488,13 +1609,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -1503,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -1515,13 +1636,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -1530,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -1542,13 +1663,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -1557,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -1568,26 +1689,54 @@
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="12">
+        <v>120</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="12">
+        <v>120</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
@@ -3062,26 +3211,55 @@
       <c r="J124" s="12"/>
       <c r="K124" s="12"/>
     </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="1"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="12"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="1"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="5"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B124">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B126">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -3100,7 +3278,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D124</xm:sqref>
+          <xm:sqref>D4:D126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -3109,7 +3287,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E124</xm:sqref>
+          <xm:sqref>E4:E126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -3118,7 +3296,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F124</xm:sqref>
+          <xm:sqref>F4:F126</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3128,7 +3306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -3141,100 +3319,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -3242,12 +3379,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -3255,13 +3388,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -3270,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -3282,13 +3415,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -3297,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -3309,13 +3442,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -3324,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -3336,13 +3469,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -3351,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -3363,13 +3496,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -3378,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -3389,26 +3522,54 @@
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="12">
+        <v>120</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="12">
+        <v>120</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
@@ -4883,26 +5044,55 @@
       <c r="J124" s="12"/>
       <c r="K124" s="12"/>
     </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="1"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="12"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="1"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B124">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B126">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4920,7 +5110,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F124</xm:sqref>
+          <xm:sqref>F4:F126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4929,7 +5119,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E124</xm:sqref>
+          <xm:sqref>E4:E126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4938,7 +5128,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D124</xm:sqref>
+          <xm:sqref>D4:D126</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4948,7 +5138,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -4961,100 +5151,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -5062,12 +5211,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -5075,13 +5220,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -5090,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -5102,13 +5247,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -5117,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -5129,13 +5274,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -5144,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -5156,13 +5301,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -5171,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -5183,13 +5328,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -5198,7 +5343,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -5209,26 +5354,54 @@
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="12">
+        <v>120</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="12">
+        <v>120</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
@@ -6703,26 +6876,55 @@
       <c r="J124" s="12"/>
       <c r="K124" s="12"/>
     </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="1"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="12"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="1"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B124">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B126">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -6740,7 +6942,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D124</xm:sqref>
+          <xm:sqref>D4:D126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -6749,7 +6951,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E124</xm:sqref>
+          <xm:sqref>E4:E126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -6758,7 +6960,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F124</xm:sqref>
+          <xm:sqref>F4:F126</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6768,7 +6970,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -6781,100 +6983,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -6882,12 +7043,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -6895,13 +7052,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -6910,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -6922,13 +7079,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -6937,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -6949,13 +7106,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -6964,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -6976,13 +7133,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -6991,7 +7148,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -7003,13 +7160,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -7018,7 +7175,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -7029,26 +7186,54 @@
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="12">
+        <v>120</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="12">
+        <v>120</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
@@ -8523,26 +8708,55 @@
       <c r="J124" s="12"/>
       <c r="K124" s="12"/>
     </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="1"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="12"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="1"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I124">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I126">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B124">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B126">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8560,7 +8774,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F124</xm:sqref>
+          <xm:sqref>F4:F126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8569,7 +8783,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E124</xm:sqref>
+          <xm:sqref>E4:E126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8578,7 +8792,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D124</xm:sqref>
+          <xm:sqref>D4:D126</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8588,7 +8802,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -8601,100 +8815,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -8702,12 +8875,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -8715,13 +8884,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -8730,7 +8899,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -8742,13 +8911,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -8757,7 +8926,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -8769,13 +8938,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -8784,7 +8953,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -8795,26 +8964,54 @@
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="12">
+        <v>120</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
@@ -10289,26 +10486,55 @@
       <c r="J122" s="12"/>
       <c r="K122" s="12"/>
     </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="1"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B122">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B124">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -10326,7 +10552,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D122</xm:sqref>
+          <xm:sqref>D4:D124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -10335,7 +10561,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E122</xm:sqref>
+          <xm:sqref>E4:E124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -10344,7 +10570,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F122</xm:sqref>
+          <xm:sqref>F4:F124</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10354,7 +10580,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -10367,100 +10593,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -10468,12 +10653,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -10481,13 +10662,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -10496,7 +10677,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -10508,13 +10689,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -10523,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -10535,13 +10716,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -10550,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -10561,26 +10742,54 @@
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="12">
+        <v>120</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
@@ -12055,26 +12264,55 @@
       <c r="J122" s="12"/>
       <c r="K122" s="12"/>
     </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="1"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I122">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I124">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B122">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B124">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12092,7 +12330,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F122</xm:sqref>
+          <xm:sqref>F4:F124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -12101,7 +12339,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E122</xm:sqref>
+          <xm:sqref>E4:E124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -12110,7 +12348,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D122</xm:sqref>
+          <xm:sqref>D4:D124</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12120,7 +12358,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -12133,100 +12371,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -12234,12 +12431,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -12247,13 +12440,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -12262,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -12274,13 +12467,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -12289,7 +12482,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -12300,26 +12493,54 @@
       <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="A7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="12">
+        <v>120</v>
+      </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -13794,26 +14015,55 @@
       <c r="J121" s="12"/>
       <c r="K121" s="12"/>
     </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="1"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B121">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B123">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -13831,7 +14081,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F121</xm:sqref>
+          <xm:sqref>F4:F123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -13840,7 +14090,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E121</xm:sqref>
+          <xm:sqref>E4:E123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -13849,7 +14099,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D121</xm:sqref>
+          <xm:sqref>D4:D123</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13859,7 +14109,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -13872,100 +14122,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B4" s="12">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11" s="11" customFormat="1">
-      <c r="A3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-    </row>
-    <row r="4" spans="1:11" s="11" customFormat="1">
-      <c r="A4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="12">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -13973,26 +14182,22 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
     </row>
-    <row r="5" spans="1:11" s="11" customFormat="1">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -14001,7 +14206,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -14011,15 +14216,15 @@
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
     </row>
-    <row r="6" spans="1:11" s="11" customFormat="1">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -14028,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -14038,33 +14243,61 @@
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
     </row>
-    <row r="7" spans="1:11" s="11" customFormat="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="12">
+        <v>120</v>
+      </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
-    <row r="8" spans="1:11" s="11" customFormat="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" s="11" customFormat="1">
+    <row r="9" spans="1:11">
       <c r="A9" s="1"/>
       <c r="B9" s="12"/>
       <c r="C9" s="2"/>
@@ -14077,7 +14310,7 @@
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" s="11" customFormat="1">
+    <row r="10" spans="1:11">
       <c r="A10" s="1"/>
       <c r="B10" s="12"/>
       <c r="C10" s="2"/>
@@ -14090,7 +14323,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" s="11" customFormat="1">
+    <row r="11" spans="1:11">
       <c r="A11" s="1"/>
       <c r="B11" s="12"/>
       <c r="C11" s="2"/>
@@ -14103,7 +14336,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" s="11" customFormat="1">
+    <row r="12" spans="1:11">
       <c r="A12" s="1"/>
       <c r="B12" s="12"/>
       <c r="C12" s="2"/>
@@ -14116,7 +14349,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" s="11" customFormat="1">
+    <row r="13" spans="1:11">
       <c r="A13" s="1"/>
       <c r="B13" s="12"/>
       <c r="C13" s="2"/>
@@ -14129,7 +14362,7 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" s="11" customFormat="1">
+    <row r="14" spans="1:11">
       <c r="A14" s="1"/>
       <c r="B14" s="12"/>
       <c r="C14" s="2"/>
@@ -14142,7 +14375,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" s="11" customFormat="1">
+    <row r="15" spans="1:11">
       <c r="A15" s="1"/>
       <c r="B15" s="12"/>
       <c r="C15" s="2"/>
@@ -14155,7 +14388,7 @@
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" s="11" customFormat="1">
+    <row r="16" spans="1:11">
       <c r="A16" s="1"/>
       <c r="B16" s="12"/>
       <c r="C16" s="2"/>
@@ -14168,7 +14401,7 @@
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" s="11" customFormat="1">
+    <row r="17" spans="1:11">
       <c r="A17" s="1"/>
       <c r="B17" s="12"/>
       <c r="C17" s="2"/>
@@ -14181,7 +14414,7 @@
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" s="11" customFormat="1">
+    <row r="18" spans="1:11">
       <c r="A18" s="1"/>
       <c r="B18" s="12"/>
       <c r="C18" s="2"/>
@@ -14194,7 +14427,7 @@
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" s="11" customFormat="1">
+    <row r="19" spans="1:11">
       <c r="A19" s="1"/>
       <c r="B19" s="12"/>
       <c r="C19" s="2"/>
@@ -14207,7 +14440,7 @@
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" s="11" customFormat="1">
+    <row r="20" spans="1:11">
       <c r="A20" s="1"/>
       <c r="B20" s="12"/>
       <c r="C20" s="2"/>
@@ -14220,7 +14453,7 @@
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" s="11" customFormat="1">
+    <row r="21" spans="1:11">
       <c r="A21" s="1"/>
       <c r="B21" s="12"/>
       <c r="C21" s="2"/>
@@ -14233,7 +14466,7 @@
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" s="11" customFormat="1">
+    <row r="22" spans="1:11">
       <c r="A22" s="1"/>
       <c r="B22" s="12"/>
       <c r="C22" s="2"/>
@@ -14246,7 +14479,7 @@
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
     </row>
-    <row r="23" spans="1:11" s="11" customFormat="1">
+    <row r="23" spans="1:11">
       <c r="A23" s="1"/>
       <c r="B23" s="12"/>
       <c r="C23" s="2"/>
@@ -14259,7 +14492,7 @@
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="1:11" s="11" customFormat="1">
+    <row r="24" spans="1:11">
       <c r="A24" s="1"/>
       <c r="B24" s="12"/>
       <c r="C24" s="2"/>
@@ -14272,7 +14505,7 @@
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:11" s="11" customFormat="1">
+    <row r="25" spans="1:11">
       <c r="A25" s="1"/>
       <c r="B25" s="12"/>
       <c r="C25" s="2"/>
@@ -14285,7 +14518,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:11" s="11" customFormat="1">
+    <row r="26" spans="1:11">
       <c r="A26" s="1"/>
       <c r="B26" s="12"/>
       <c r="C26" s="2"/>
@@ -14298,7 +14531,7 @@
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
     </row>
-    <row r="27" spans="1:11" s="11" customFormat="1">
+    <row r="27" spans="1:11">
       <c r="A27" s="1"/>
       <c r="B27" s="12"/>
       <c r="C27" s="2"/>
@@ -14311,7 +14544,7 @@
       <c r="J27" s="12"/>
       <c r="K27" s="12"/>
     </row>
-    <row r="28" spans="1:11" s="11" customFormat="1">
+    <row r="28" spans="1:11">
       <c r="A28" s="1"/>
       <c r="B28" s="12"/>
       <c r="C28" s="2"/>
@@ -14324,7 +14557,7 @@
       <c r="J28" s="12"/>
       <c r="K28" s="12"/>
     </row>
-    <row r="29" spans="1:11" s="11" customFormat="1">
+    <row r="29" spans="1:11">
       <c r="A29" s="1"/>
       <c r="B29" s="12"/>
       <c r="C29" s="2"/>
@@ -14337,7 +14570,7 @@
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
     </row>
-    <row r="30" spans="1:11" s="11" customFormat="1">
+    <row r="30" spans="1:11">
       <c r="A30" s="1"/>
       <c r="B30" s="12"/>
       <c r="C30" s="2"/>
@@ -14350,7 +14583,7 @@
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" spans="1:11" s="11" customFormat="1">
+    <row r="31" spans="1:11">
       <c r="A31" s="1"/>
       <c r="B31" s="12"/>
       <c r="C31" s="2"/>
@@ -14363,7 +14596,7 @@
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
     </row>
-    <row r="32" spans="1:11" s="11" customFormat="1">
+    <row r="32" spans="1:11">
       <c r="A32" s="1"/>
       <c r="B32" s="12"/>
       <c r="C32" s="2"/>
@@ -14376,7 +14609,7 @@
       <c r="J32" s="12"/>
       <c r="K32" s="12"/>
     </row>
-    <row r="33" spans="1:11" s="11" customFormat="1">
+    <row r="33" spans="1:11">
       <c r="A33" s="1"/>
       <c r="B33" s="12"/>
       <c r="C33" s="2"/>
@@ -14389,7 +14622,7 @@
       <c r="J33" s="12"/>
       <c r="K33" s="12"/>
     </row>
-    <row r="34" spans="1:11" s="11" customFormat="1">
+    <row r="34" spans="1:11">
       <c r="A34" s="1"/>
       <c r="B34" s="12"/>
       <c r="C34" s="2"/>
@@ -14402,7 +14635,7 @@
       <c r="J34" s="12"/>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" s="11" customFormat="1">
+    <row r="35" spans="1:11">
       <c r="A35" s="1"/>
       <c r="B35" s="12"/>
       <c r="C35" s="2"/>
@@ -14415,7 +14648,7 @@
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
     </row>
-    <row r="36" spans="1:11" s="11" customFormat="1">
+    <row r="36" spans="1:11">
       <c r="A36" s="1"/>
       <c r="B36" s="12"/>
       <c r="C36" s="2"/>
@@ -14428,7 +14661,7 @@
       <c r="J36" s="12"/>
       <c r="K36" s="12"/>
     </row>
-    <row r="37" spans="1:11" s="11" customFormat="1">
+    <row r="37" spans="1:11">
       <c r="A37" s="1"/>
       <c r="B37" s="12"/>
       <c r="C37" s="2"/>
@@ -14441,7 +14674,7 @@
       <c r="J37" s="12"/>
       <c r="K37" s="12"/>
     </row>
-    <row r="38" spans="1:11" s="11" customFormat="1">
+    <row r="38" spans="1:11">
       <c r="A38" s="1"/>
       <c r="B38" s="12"/>
       <c r="C38" s="2"/>
@@ -14454,7 +14687,7 @@
       <c r="J38" s="12"/>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="1:11" s="11" customFormat="1">
+    <row r="39" spans="1:11">
       <c r="A39" s="1"/>
       <c r="B39" s="12"/>
       <c r="C39" s="2"/>
@@ -14467,7 +14700,7 @@
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
     </row>
-    <row r="40" spans="1:11" s="11" customFormat="1">
+    <row r="40" spans="1:11">
       <c r="A40" s="1"/>
       <c r="B40" s="12"/>
       <c r="C40" s="2"/>
@@ -14480,7 +14713,7 @@
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
     </row>
-    <row r="41" spans="1:11" s="11" customFormat="1">
+    <row r="41" spans="1:11">
       <c r="A41" s="1"/>
       <c r="B41" s="12"/>
       <c r="C41" s="2"/>
@@ -14493,7 +14726,7 @@
       <c r="J41" s="12"/>
       <c r="K41" s="12"/>
     </row>
-    <row r="42" spans="1:11" s="11" customFormat="1">
+    <row r="42" spans="1:11">
       <c r="A42" s="1"/>
       <c r="B42" s="12"/>
       <c r="C42" s="2"/>
@@ -14506,7 +14739,7 @@
       <c r="J42" s="12"/>
       <c r="K42" s="12"/>
     </row>
-    <row r="43" spans="1:11" s="11" customFormat="1">
+    <row r="43" spans="1:11">
       <c r="A43" s="1"/>
       <c r="B43" s="12"/>
       <c r="C43" s="2"/>
@@ -14519,7 +14752,7 @@
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
     </row>
-    <row r="44" spans="1:11" s="11" customFormat="1">
+    <row r="44" spans="1:11">
       <c r="A44" s="1"/>
       <c r="B44" s="12"/>
       <c r="C44" s="2"/>
@@ -14532,7 +14765,7 @@
       <c r="J44" s="12"/>
       <c r="K44" s="12"/>
     </row>
-    <row r="45" spans="1:11" s="11" customFormat="1">
+    <row r="45" spans="1:11">
       <c r="A45" s="1"/>
       <c r="B45" s="12"/>
       <c r="C45" s="2"/>
@@ -14545,7 +14778,7 @@
       <c r="J45" s="12"/>
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="1:11" s="11" customFormat="1">
+    <row r="46" spans="1:11">
       <c r="A46" s="1"/>
       <c r="B46" s="12"/>
       <c r="C46" s="2"/>
@@ -14558,7 +14791,7 @@
       <c r="J46" s="12"/>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="1:11" s="11" customFormat="1">
+    <row r="47" spans="1:11">
       <c r="A47" s="1"/>
       <c r="B47" s="12"/>
       <c r="C47" s="2"/>
@@ -14571,7 +14804,7 @@
       <c r="J47" s="12"/>
       <c r="K47" s="12"/>
     </row>
-    <row r="48" spans="1:11" s="11" customFormat="1">
+    <row r="48" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="12"/>
       <c r="C48" s="2"/>
@@ -14584,7 +14817,7 @@
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" spans="1:11" s="11" customFormat="1">
+    <row r="49" spans="1:11">
       <c r="A49" s="1"/>
       <c r="B49" s="12"/>
       <c r="C49" s="2"/>
@@ -14597,7 +14830,7 @@
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
     </row>
-    <row r="50" spans="1:11" s="11" customFormat="1">
+    <row r="50" spans="1:11">
       <c r="A50" s="1"/>
       <c r="B50" s="12"/>
       <c r="C50" s="2"/>
@@ -14610,7 +14843,7 @@
       <c r="J50" s="12"/>
       <c r="K50" s="12"/>
     </row>
-    <row r="51" spans="1:11" s="11" customFormat="1">
+    <row r="51" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="12"/>
       <c r="C51" s="2"/>
@@ -14623,7 +14856,7 @@
       <c r="J51" s="12"/>
       <c r="K51" s="12"/>
     </row>
-    <row r="52" spans="1:11" s="11" customFormat="1">
+    <row r="52" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="12"/>
       <c r="C52" s="2"/>
@@ -14636,7 +14869,7 @@
       <c r="J52" s="12"/>
       <c r="K52" s="12"/>
     </row>
-    <row r="53" spans="1:11" s="11" customFormat="1">
+    <row r="53" spans="1:11">
       <c r="A53" s="1"/>
       <c r="B53" s="12"/>
       <c r="C53" s="2"/>
@@ -14649,7 +14882,7 @@
       <c r="J53" s="12"/>
       <c r="K53" s="12"/>
     </row>
-    <row r="54" spans="1:11" s="11" customFormat="1">
+    <row r="54" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="12"/>
       <c r="C54" s="2"/>
@@ -14662,7 +14895,7 @@
       <c r="J54" s="12"/>
       <c r="K54" s="12"/>
     </row>
-    <row r="55" spans="1:11" s="11" customFormat="1">
+    <row r="55" spans="1:11">
       <c r="A55" s="1"/>
       <c r="B55" s="12"/>
       <c r="C55" s="2"/>
@@ -14675,7 +14908,7 @@
       <c r="J55" s="12"/>
       <c r="K55" s="12"/>
     </row>
-    <row r="56" spans="1:11" s="11" customFormat="1">
+    <row r="56" spans="1:11">
       <c r="A56" s="1"/>
       <c r="B56" s="12"/>
       <c r="C56" s="2"/>
@@ -14688,7 +14921,7 @@
       <c r="J56" s="12"/>
       <c r="K56" s="12"/>
     </row>
-    <row r="57" spans="1:11" s="11" customFormat="1">
+    <row r="57" spans="1:11">
       <c r="A57" s="1"/>
       <c r="B57" s="12"/>
       <c r="C57" s="2"/>
@@ -14701,7 +14934,7 @@
       <c r="J57" s="12"/>
       <c r="K57" s="12"/>
     </row>
-    <row r="58" spans="1:11" s="11" customFormat="1">
+    <row r="58" spans="1:11">
       <c r="A58" s="1"/>
       <c r="B58" s="12"/>
       <c r="C58" s="2"/>
@@ -14714,7 +14947,7 @@
       <c r="J58" s="12"/>
       <c r="K58" s="12"/>
     </row>
-    <row r="59" spans="1:11" s="11" customFormat="1">
+    <row r="59" spans="1:11">
       <c r="A59" s="1"/>
       <c r="B59" s="12"/>
       <c r="C59" s="2"/>
@@ -14727,7 +14960,7 @@
       <c r="J59" s="12"/>
       <c r="K59" s="12"/>
     </row>
-    <row r="60" spans="1:11" s="11" customFormat="1">
+    <row r="60" spans="1:11">
       <c r="A60" s="1"/>
       <c r="B60" s="12"/>
       <c r="C60" s="2"/>
@@ -14740,7 +14973,7 @@
       <c r="J60" s="12"/>
       <c r="K60" s="12"/>
     </row>
-    <row r="61" spans="1:11" s="11" customFormat="1">
+    <row r="61" spans="1:11">
       <c r="A61" s="1"/>
       <c r="B61" s="12"/>
       <c r="C61" s="2"/>
@@ -14753,7 +14986,7 @@
       <c r="J61" s="12"/>
       <c r="K61" s="12"/>
     </row>
-    <row r="62" spans="1:11" s="11" customFormat="1">
+    <row r="62" spans="1:11">
       <c r="A62" s="1"/>
       <c r="B62" s="12"/>
       <c r="C62" s="2"/>
@@ -14766,7 +14999,7 @@
       <c r="J62" s="12"/>
       <c r="K62" s="12"/>
     </row>
-    <row r="63" spans="1:11" s="11" customFormat="1">
+    <row r="63" spans="1:11">
       <c r="A63" s="1"/>
       <c r="B63" s="12"/>
       <c r="C63" s="2"/>
@@ -14779,7 +15012,7 @@
       <c r="J63" s="12"/>
       <c r="K63" s="12"/>
     </row>
-    <row r="64" spans="1:11" s="11" customFormat="1">
+    <row r="64" spans="1:11">
       <c r="A64" s="1"/>
       <c r="B64" s="12"/>
       <c r="C64" s="2"/>
@@ -14792,7 +15025,7 @@
       <c r="J64" s="12"/>
       <c r="K64" s="12"/>
     </row>
-    <row r="65" spans="1:11" s="11" customFormat="1">
+    <row r="65" spans="1:11">
       <c r="A65" s="1"/>
       <c r="B65" s="12"/>
       <c r="C65" s="2"/>
@@ -14805,7 +15038,7 @@
       <c r="J65" s="12"/>
       <c r="K65" s="12"/>
     </row>
-    <row r="66" spans="1:11" s="11" customFormat="1">
+    <row r="66" spans="1:11">
       <c r="A66" s="1"/>
       <c r="B66" s="12"/>
       <c r="C66" s="2"/>
@@ -14818,7 +15051,7 @@
       <c r="J66" s="12"/>
       <c r="K66" s="12"/>
     </row>
-    <row r="67" spans="1:11" s="11" customFormat="1">
+    <row r="67" spans="1:11">
       <c r="A67" s="1"/>
       <c r="B67" s="12"/>
       <c r="C67" s="2"/>
@@ -14831,7 +15064,7 @@
       <c r="J67" s="12"/>
       <c r="K67" s="12"/>
     </row>
-    <row r="68" spans="1:11" s="11" customFormat="1">
+    <row r="68" spans="1:11">
       <c r="A68" s="1"/>
       <c r="B68" s="12"/>
       <c r="C68" s="2"/>
@@ -14844,7 +15077,7 @@
       <c r="J68" s="12"/>
       <c r="K68" s="12"/>
     </row>
-    <row r="69" spans="1:11" s="11" customFormat="1">
+    <row r="69" spans="1:11">
       <c r="A69" s="1"/>
       <c r="B69" s="12"/>
       <c r="C69" s="2"/>
@@ -14857,7 +15090,7 @@
       <c r="J69" s="12"/>
       <c r="K69" s="12"/>
     </row>
-    <row r="70" spans="1:11" s="11" customFormat="1">
+    <row r="70" spans="1:11">
       <c r="A70" s="1"/>
       <c r="B70" s="12"/>
       <c r="C70" s="2"/>
@@ -14870,7 +15103,7 @@
       <c r="J70" s="12"/>
       <c r="K70" s="12"/>
     </row>
-    <row r="71" spans="1:11" s="11" customFormat="1">
+    <row r="71" spans="1:11">
       <c r="A71" s="1"/>
       <c r="B71" s="12"/>
       <c r="C71" s="2"/>
@@ -14883,7 +15116,7 @@
       <c r="J71" s="12"/>
       <c r="K71" s="12"/>
     </row>
-    <row r="72" spans="1:11" s="11" customFormat="1">
+    <row r="72" spans="1:11">
       <c r="A72" s="1"/>
       <c r="B72" s="12"/>
       <c r="C72" s="2"/>
@@ -14896,7 +15129,7 @@
       <c r="J72" s="12"/>
       <c r="K72" s="12"/>
     </row>
-    <row r="73" spans="1:11" s="11" customFormat="1">
+    <row r="73" spans="1:11">
       <c r="A73" s="1"/>
       <c r="B73" s="12"/>
       <c r="C73" s="2"/>
@@ -14909,7 +15142,7 @@
       <c r="J73" s="12"/>
       <c r="K73" s="12"/>
     </row>
-    <row r="74" spans="1:11" s="11" customFormat="1">
+    <row r="74" spans="1:11">
       <c r="A74" s="1"/>
       <c r="B74" s="12"/>
       <c r="C74" s="2"/>
@@ -14922,7 +15155,7 @@
       <c r="J74" s="12"/>
       <c r="K74" s="12"/>
     </row>
-    <row r="75" spans="1:11" s="11" customFormat="1">
+    <row r="75" spans="1:11">
       <c r="A75" s="1"/>
       <c r="B75" s="12"/>
       <c r="C75" s="2"/>
@@ -14935,7 +15168,7 @@
       <c r="J75" s="12"/>
       <c r="K75" s="12"/>
     </row>
-    <row r="76" spans="1:11" s="11" customFormat="1">
+    <row r="76" spans="1:11">
       <c r="A76" s="1"/>
       <c r="B76" s="12"/>
       <c r="C76" s="2"/>
@@ -14948,7 +15181,7 @@
       <c r="J76" s="12"/>
       <c r="K76" s="12"/>
     </row>
-    <row r="77" spans="1:11" s="11" customFormat="1">
+    <row r="77" spans="1:11">
       <c r="A77" s="1"/>
       <c r="B77" s="12"/>
       <c r="C77" s="2"/>
@@ -14961,7 +15194,7 @@
       <c r="J77" s="12"/>
       <c r="K77" s="12"/>
     </row>
-    <row r="78" spans="1:11" s="11" customFormat="1">
+    <row r="78" spans="1:11">
       <c r="A78" s="1"/>
       <c r="B78" s="12"/>
       <c r="C78" s="2"/>
@@ -14974,7 +15207,7 @@
       <c r="J78" s="12"/>
       <c r="K78" s="12"/>
     </row>
-    <row r="79" spans="1:11" s="11" customFormat="1">
+    <row r="79" spans="1:11">
       <c r="A79" s="1"/>
       <c r="B79" s="12"/>
       <c r="C79" s="2"/>
@@ -14987,7 +15220,7 @@
       <c r="J79" s="12"/>
       <c r="K79" s="12"/>
     </row>
-    <row r="80" spans="1:11" s="11" customFormat="1">
+    <row r="80" spans="1:11">
       <c r="A80" s="1"/>
       <c r="B80" s="12"/>
       <c r="C80" s="2"/>
@@ -15000,7 +15233,7 @@
       <c r="J80" s="12"/>
       <c r="K80" s="12"/>
     </row>
-    <row r="81" spans="1:11" s="11" customFormat="1">
+    <row r="81" spans="1:11">
       <c r="A81" s="1"/>
       <c r="B81" s="12"/>
       <c r="C81" s="2"/>
@@ -15013,7 +15246,7 @@
       <c r="J81" s="12"/>
       <c r="K81" s="12"/>
     </row>
-    <row r="82" spans="1:11" s="11" customFormat="1">
+    <row r="82" spans="1:11">
       <c r="A82" s="1"/>
       <c r="B82" s="12"/>
       <c r="C82" s="2"/>
@@ -15026,7 +15259,7 @@
       <c r="J82" s="12"/>
       <c r="K82" s="12"/>
     </row>
-    <row r="83" spans="1:11" s="11" customFormat="1">
+    <row r="83" spans="1:11">
       <c r="A83" s="1"/>
       <c r="B83" s="12"/>
       <c r="C83" s="2"/>
@@ -15039,7 +15272,7 @@
       <c r="J83" s="12"/>
       <c r="K83" s="12"/>
     </row>
-    <row r="84" spans="1:11" s="11" customFormat="1">
+    <row r="84" spans="1:11">
       <c r="A84" s="1"/>
       <c r="B84" s="12"/>
       <c r="C84" s="2"/>
@@ -15052,7 +15285,7 @@
       <c r="J84" s="12"/>
       <c r="K84" s="12"/>
     </row>
-    <row r="85" spans="1:11" s="11" customFormat="1">
+    <row r="85" spans="1:11">
       <c r="A85" s="1"/>
       <c r="B85" s="12"/>
       <c r="C85" s="2"/>
@@ -15065,7 +15298,7 @@
       <c r="J85" s="12"/>
       <c r="K85" s="12"/>
     </row>
-    <row r="86" spans="1:11" s="11" customFormat="1">
+    <row r="86" spans="1:11">
       <c r="A86" s="1"/>
       <c r="B86" s="12"/>
       <c r="C86" s="2"/>
@@ -15078,7 +15311,7 @@
       <c r="J86" s="12"/>
       <c r="K86" s="12"/>
     </row>
-    <row r="87" spans="1:11" s="11" customFormat="1">
+    <row r="87" spans="1:11">
       <c r="A87" s="1"/>
       <c r="B87" s="12"/>
       <c r="C87" s="2"/>
@@ -15091,7 +15324,7 @@
       <c r="J87" s="12"/>
       <c r="K87" s="12"/>
     </row>
-    <row r="88" spans="1:11" s="11" customFormat="1">
+    <row r="88" spans="1:11">
       <c r="A88" s="1"/>
       <c r="B88" s="12"/>
       <c r="C88" s="2"/>
@@ -15104,7 +15337,7 @@
       <c r="J88" s="12"/>
       <c r="K88" s="12"/>
     </row>
-    <row r="89" spans="1:11" s="11" customFormat="1">
+    <row r="89" spans="1:11">
       <c r="A89" s="1"/>
       <c r="B89" s="12"/>
       <c r="C89" s="2"/>
@@ -15117,7 +15350,7 @@
       <c r="J89" s="12"/>
       <c r="K89" s="12"/>
     </row>
-    <row r="90" spans="1:11" s="11" customFormat="1">
+    <row r="90" spans="1:11">
       <c r="A90" s="1"/>
       <c r="B90" s="12"/>
       <c r="C90" s="2"/>
@@ -15130,7 +15363,7 @@
       <c r="J90" s="12"/>
       <c r="K90" s="12"/>
     </row>
-    <row r="91" spans="1:11" s="11" customFormat="1">
+    <row r="91" spans="1:11">
       <c r="A91" s="1"/>
       <c r="B91" s="12"/>
       <c r="C91" s="2"/>
@@ -15143,7 +15376,7 @@
       <c r="J91" s="12"/>
       <c r="K91" s="12"/>
     </row>
-    <row r="92" spans="1:11" s="11" customFormat="1">
+    <row r="92" spans="1:11">
       <c r="A92" s="1"/>
       <c r="B92" s="12"/>
       <c r="C92" s="2"/>
@@ -15156,7 +15389,7 @@
       <c r="J92" s="12"/>
       <c r="K92" s="12"/>
     </row>
-    <row r="93" spans="1:11" s="11" customFormat="1">
+    <row r="93" spans="1:11">
       <c r="A93" s="1"/>
       <c r="B93" s="12"/>
       <c r="C93" s="2"/>
@@ -15169,7 +15402,7 @@
       <c r="J93" s="12"/>
       <c r="K93" s="12"/>
     </row>
-    <row r="94" spans="1:11" s="11" customFormat="1">
+    <row r="94" spans="1:11">
       <c r="A94" s="1"/>
       <c r="B94" s="12"/>
       <c r="C94" s="2"/>
@@ -15182,7 +15415,7 @@
       <c r="J94" s="12"/>
       <c r="K94" s="12"/>
     </row>
-    <row r="95" spans="1:11" s="11" customFormat="1">
+    <row r="95" spans="1:11">
       <c r="A95" s="1"/>
       <c r="B95" s="12"/>
       <c r="C95" s="2"/>
@@ -15195,7 +15428,7 @@
       <c r="J95" s="12"/>
       <c r="K95" s="12"/>
     </row>
-    <row r="96" spans="1:11" s="11" customFormat="1">
+    <row r="96" spans="1:11">
       <c r="A96" s="1"/>
       <c r="B96" s="12"/>
       <c r="C96" s="2"/>
@@ -15208,7 +15441,7 @@
       <c r="J96" s="12"/>
       <c r="K96" s="12"/>
     </row>
-    <row r="97" spans="1:11" s="11" customFormat="1">
+    <row r="97" spans="1:11">
       <c r="A97" s="1"/>
       <c r="B97" s="12"/>
       <c r="C97" s="2"/>
@@ -15221,7 +15454,7 @@
       <c r="J97" s="12"/>
       <c r="K97" s="12"/>
     </row>
-    <row r="98" spans="1:11" s="11" customFormat="1">
+    <row r="98" spans="1:11">
       <c r="A98" s="1"/>
       <c r="B98" s="12"/>
       <c r="C98" s="2"/>
@@ -15234,7 +15467,7 @@
       <c r="J98" s="12"/>
       <c r="K98" s="12"/>
     </row>
-    <row r="99" spans="1:11" s="11" customFormat="1">
+    <row r="99" spans="1:11">
       <c r="A99" s="1"/>
       <c r="B99" s="12"/>
       <c r="C99" s="2"/>
@@ -15247,7 +15480,7 @@
       <c r="J99" s="12"/>
       <c r="K99" s="12"/>
     </row>
-    <row r="100" spans="1:11" s="11" customFormat="1">
+    <row r="100" spans="1:11">
       <c r="A100" s="1"/>
       <c r="B100" s="12"/>
       <c r="C100" s="2"/>
@@ -15260,7 +15493,7 @@
       <c r="J100" s="12"/>
       <c r="K100" s="12"/>
     </row>
-    <row r="101" spans="1:11" s="11" customFormat="1">
+    <row r="101" spans="1:11">
       <c r="A101" s="1"/>
       <c r="B101" s="12"/>
       <c r="C101" s="2"/>
@@ -15273,7 +15506,7 @@
       <c r="J101" s="12"/>
       <c r="K101" s="12"/>
     </row>
-    <row r="102" spans="1:11" s="11" customFormat="1">
+    <row r="102" spans="1:11">
       <c r="A102" s="1"/>
       <c r="B102" s="12"/>
       <c r="C102" s="2"/>
@@ -15286,7 +15519,7 @@
       <c r="J102" s="12"/>
       <c r="K102" s="12"/>
     </row>
-    <row r="103" spans="1:11" s="11" customFormat="1">
+    <row r="103" spans="1:11">
       <c r="A103" s="1"/>
       <c r="B103" s="12"/>
       <c r="C103" s="2"/>
@@ -15299,7 +15532,7 @@
       <c r="J103" s="12"/>
       <c r="K103" s="12"/>
     </row>
-    <row r="104" spans="1:11" s="11" customFormat="1">
+    <row r="104" spans="1:11">
       <c r="A104" s="1"/>
       <c r="B104" s="12"/>
       <c r="C104" s="2"/>
@@ -15312,7 +15545,7 @@
       <c r="J104" s="12"/>
       <c r="K104" s="12"/>
     </row>
-    <row r="105" spans="1:11" s="11" customFormat="1">
+    <row r="105" spans="1:11">
       <c r="A105" s="1"/>
       <c r="B105" s="12"/>
       <c r="C105" s="2"/>
@@ -15325,7 +15558,7 @@
       <c r="J105" s="12"/>
       <c r="K105" s="12"/>
     </row>
-    <row r="106" spans="1:11" s="11" customFormat="1">
+    <row r="106" spans="1:11">
       <c r="A106" s="1"/>
       <c r="B106" s="12"/>
       <c r="C106" s="2"/>
@@ -15338,7 +15571,7 @@
       <c r="J106" s="12"/>
       <c r="K106" s="12"/>
     </row>
-    <row r="107" spans="1:11" s="11" customFormat="1">
+    <row r="107" spans="1:11">
       <c r="A107" s="1"/>
       <c r="B107" s="12"/>
       <c r="C107" s="2"/>
@@ -15351,7 +15584,7 @@
       <c r="J107" s="12"/>
       <c r="K107" s="12"/>
     </row>
-    <row r="108" spans="1:11" s="11" customFormat="1">
+    <row r="108" spans="1:11">
       <c r="A108" s="1"/>
       <c r="B108" s="12"/>
       <c r="C108" s="2"/>
@@ -15364,7 +15597,7 @@
       <c r="J108" s="12"/>
       <c r="K108" s="12"/>
     </row>
-    <row r="109" spans="1:11" s="11" customFormat="1">
+    <row r="109" spans="1:11">
       <c r="A109" s="1"/>
       <c r="B109" s="12"/>
       <c r="C109" s="2"/>
@@ -15377,7 +15610,7 @@
       <c r="J109" s="12"/>
       <c r="K109" s="12"/>
     </row>
-    <row r="110" spans="1:11" s="11" customFormat="1">
+    <row r="110" spans="1:11">
       <c r="A110" s="1"/>
       <c r="B110" s="12"/>
       <c r="C110" s="2"/>
@@ -15390,7 +15623,7 @@
       <c r="J110" s="12"/>
       <c r="K110" s="12"/>
     </row>
-    <row r="111" spans="1:11" s="11" customFormat="1">
+    <row r="111" spans="1:11">
       <c r="A111" s="1"/>
       <c r="B111" s="12"/>
       <c r="C111" s="2"/>
@@ -15403,7 +15636,7 @@
       <c r="J111" s="12"/>
       <c r="K111" s="12"/>
     </row>
-    <row r="112" spans="1:11" s="11" customFormat="1">
+    <row r="112" spans="1:11">
       <c r="A112" s="1"/>
       <c r="B112" s="12"/>
       <c r="C112" s="2"/>
@@ -15416,7 +15649,7 @@
       <c r="J112" s="12"/>
       <c r="K112" s="12"/>
     </row>
-    <row r="113" spans="1:11" s="11" customFormat="1">
+    <row r="113" spans="1:11">
       <c r="A113" s="1"/>
       <c r="B113" s="12"/>
       <c r="C113" s="2"/>
@@ -15429,7 +15662,7 @@
       <c r="J113" s="12"/>
       <c r="K113" s="12"/>
     </row>
-    <row r="114" spans="1:11" s="11" customFormat="1">
+    <row r="114" spans="1:11">
       <c r="A114" s="1"/>
       <c r="B114" s="12"/>
       <c r="C114" s="2"/>
@@ -15442,7 +15675,7 @@
       <c r="J114" s="12"/>
       <c r="K114" s="12"/>
     </row>
-    <row r="115" spans="1:11" s="11" customFormat="1">
+    <row r="115" spans="1:11">
       <c r="A115" s="1"/>
       <c r="B115" s="12"/>
       <c r="C115" s="2"/>
@@ -15455,7 +15688,7 @@
       <c r="J115" s="12"/>
       <c r="K115" s="12"/>
     </row>
-    <row r="116" spans="1:11" s="11" customFormat="1">
+    <row r="116" spans="1:11">
       <c r="A116" s="1"/>
       <c r="B116" s="12"/>
       <c r="C116" s="2"/>
@@ -15468,7 +15701,7 @@
       <c r="J116" s="12"/>
       <c r="K116" s="12"/>
     </row>
-    <row r="117" spans="1:11" s="11" customFormat="1">
+    <row r="117" spans="1:11">
       <c r="A117" s="1"/>
       <c r="B117" s="12"/>
       <c r="C117" s="2"/>
@@ -15481,7 +15714,7 @@
       <c r="J117" s="12"/>
       <c r="K117" s="12"/>
     </row>
-    <row r="118" spans="1:11" s="11" customFormat="1">
+    <row r="118" spans="1:11">
       <c r="A118" s="1"/>
       <c r="B118" s="12"/>
       <c r="C118" s="2"/>
@@ -15494,7 +15727,7 @@
       <c r="J118" s="12"/>
       <c r="K118" s="12"/>
     </row>
-    <row r="119" spans="1:11" s="11" customFormat="1">
+    <row r="119" spans="1:11">
       <c r="A119" s="1"/>
       <c r="B119" s="12"/>
       <c r="C119" s="2"/>
@@ -15507,7 +15740,7 @@
       <c r="J119" s="12"/>
       <c r="K119" s="12"/>
     </row>
-    <row r="120" spans="1:11" s="11" customFormat="1">
+    <row r="120" spans="1:11">
       <c r="A120" s="1"/>
       <c r="B120" s="12"/>
       <c r="C120" s="2"/>
@@ -15520,7 +15753,7 @@
       <c r="J120" s="12"/>
       <c r="K120" s="12"/>
     </row>
-    <row r="121" spans="1:11" s="11" customFormat="1">
+    <row r="121" spans="1:11">
       <c r="A121" s="1"/>
       <c r="B121" s="12"/>
       <c r="C121" s="2"/>
@@ -15533,39 +15766,55 @@
       <c r="J121" s="12"/>
       <c r="K121" s="12"/>
     </row>
-    <row r="122" spans="1:11" s="11" customFormat="1">
-      <c r="A122" s="14"/>
-      <c r="B122" s="15"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
-      <c r="H122" s="15"/>
-      <c r="I122" s="15"/>
-      <c r="J122" s="15"/>
-      <c r="K122" s="15"/>
+    <row r="122" spans="1:11">
+      <c r="A122" s="1"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B121">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B123">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -15583,7 +15832,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D121</xm:sqref>
+          <xm:sqref>D4:D123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -15592,7 +15841,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E121</xm:sqref>
+          <xm:sqref>E4:E123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -15601,7 +15850,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F121</xm:sqref>
+          <xm:sqref>F4:F123</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
